--- a/xlsx/criticalValues.xlsx
+++ b/xlsx/criticalValues.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\36306\Desktop\ERFP_SzilardPalma\Normality test\ReplicationCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F793EE-0A45-4650-A829-D023F3999236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2995C8A-EC9B-46BD-ABA5-7F22471C4305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11385" xr2:uid="{5F53AE15-6924-4C44-9D31-F7E7381805D5}"/>
+    <workbookView xWindow="7200" yWindow="4215" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{429E2E8F-ADCA-4444-BDB1-9C383A7CAE17}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
+    <sheet name="Munka1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,9 +68,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normál" xfId="0" builtinId="0"/>
@@ -383,298 +383,307 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9230ADBC-4056-4E8C-ACF0-1CE4750B1CDF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C7DF4D4-CD1C-4A3A-9A86-BEA1FAA46499}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE48116-C888-4775-A720-A197897C97FC}">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
-        <v>0.84493256151589902</v>
-      </c>
-      <c r="B1" s="1">
-        <v>0.84313599108592563</v>
-      </c>
-      <c r="C1" s="1">
-        <v>0.68591441301089695</v>
-      </c>
-      <c r="D1" s="1">
-        <v>0.1188463206647921</v>
-      </c>
-      <c r="E1" s="1">
-        <v>0.40947000815469858</v>
-      </c>
-      <c r="F1" s="1">
-        <v>2.5019149262532379</v>
-      </c>
-      <c r="G1" s="1">
-        <v>6.4801056967101029</v>
-      </c>
-      <c r="H1" s="1">
-        <v>0.8580726485915775</v>
-      </c>
-      <c r="I1" s="1">
-        <v>1.312644406977447</v>
+      <c r="A1">
+        <v>0.84432617062933779</v>
+      </c>
+      <c r="B1">
+        <v>0.84158598777000071</v>
+      </c>
+      <c r="C1">
+        <v>0.68968367533129538</v>
+      </c>
+      <c r="D1">
+        <v>0.12574190941217156</v>
+      </c>
+      <c r="E1">
+        <v>0.40938966741812721</v>
+      </c>
+      <c r="F1">
+        <v>2.5423643867118746</v>
+      </c>
+      <c r="G1">
+        <v>6.5647514629119303</v>
+      </c>
+      <c r="H1">
+        <v>0.85781635674614798</v>
+      </c>
+      <c r="I1">
+        <v>1.3064920999474152</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>0.90412092194725324</v>
-      </c>
-      <c r="B2" s="1">
-        <v>0.90278406368433117</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.72583330078911246</v>
-      </c>
-      <c r="D2" s="1">
-        <v>0.12404448951272647</v>
-      </c>
-      <c r="E2" s="1">
-        <v>0.29490540729008402</v>
-      </c>
-      <c r="F2" s="1">
-        <v>3.8115738118981439</v>
-      </c>
-      <c r="G2" s="1">
-        <v>6.3592012060749852</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0.4289414884721896</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.403041405106539</v>
+      <c r="A2">
+        <v>0.90427200497940541</v>
+      </c>
+      <c r="B2">
+        <v>0.9030343009374413</v>
+      </c>
+      <c r="C2">
+        <v>0.72336742725030234</v>
+      </c>
+      <c r="D2">
+        <v>0.12622828138726666</v>
+      </c>
+      <c r="E2">
+        <v>0.29423772816535587</v>
+      </c>
+      <c r="F2">
+        <v>3.8146304858292184</v>
+      </c>
+      <c r="G2">
+        <v>6.3859135773337528</v>
+      </c>
+      <c r="H2">
+        <v>0.42853877023312237</v>
+      </c>
+      <c r="I2">
+        <v>1.3841250667735019</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>0.93009106090511096</v>
-      </c>
-      <c r="B3" s="1">
-        <v>0.92949457713949146</v>
-      </c>
-      <c r="C3" s="1">
-        <v>0.74020300936465588</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0.12505111211189418</v>
-      </c>
-      <c r="E3" s="1">
-        <v>0.2416421995896636</v>
-      </c>
-      <c r="F3" s="1">
-        <v>4.3829091161026863</v>
-      </c>
-      <c r="G3" s="1">
-        <v>6.3450473707877286</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0.3452789194877679</v>
-      </c>
-      <c r="I3" s="1">
-        <v>3.6945026029253905</v>
+      <c r="A3">
+        <v>0.9302544387145868</v>
+      </c>
+      <c r="B3">
+        <v>0.92961019238824139</v>
+      </c>
+      <c r="C3">
+        <v>0.73277017397453292</v>
+      </c>
+      <c r="D3">
+        <v>0.12628557035602458</v>
+      </c>
+      <c r="E3">
+        <v>0.2419931636428414</v>
+      </c>
+      <c r="F3">
+        <v>4.39837933177777</v>
+      </c>
+      <c r="G3">
+        <v>6.3895903435313439</v>
+      </c>
+      <c r="H3">
+        <v>0.34515968359045002</v>
+      </c>
+      <c r="I3">
+        <v>3.6826903924815335</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>0.94446378389340202</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.9443598627946439</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.73873670286862136</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0.1249462852290448</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.21046353448979116</v>
-      </c>
-      <c r="F4" s="1">
-        <v>4.7282163532935311</v>
-      </c>
-      <c r="G4" s="1">
-        <v>6.3294529070292196</v>
-      </c>
-      <c r="H4" s="1">
-        <v>0.30065957536219146</v>
-      </c>
-      <c r="I4" s="1">
-        <v>7.7942020391067484</v>
+      <c r="A4">
+        <v>0.9446458871178508</v>
+      </c>
+      <c r="B4">
+        <v>0.9443107688119099</v>
+      </c>
+      <c r="C4">
+        <v>0.73772398181766619</v>
+      </c>
+      <c r="D4">
+        <v>0.12617278227887652</v>
+      </c>
+      <c r="E4">
+        <v>0.21036117826528128</v>
+      </c>
+      <c r="F4">
+        <v>4.759731091597561</v>
+      </c>
+      <c r="G4">
+        <v>6.3765460051995122</v>
+      </c>
+      <c r="H4">
+        <v>0.30020687835159277</v>
+      </c>
+      <c r="I4">
+        <v>7.7650864224188876</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>0.95375824013991695</v>
-      </c>
-      <c r="B5" s="1">
-        <v>0.95359313581448746</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.74818851265801811</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0.1260903307696532</v>
-      </c>
-      <c r="E5" s="1">
-        <v>0.18889307730880911</v>
-      </c>
-      <c r="F5" s="1">
-        <v>4.980749620397285</v>
-      </c>
-      <c r="G5" s="1">
-        <v>6.3936761134616384</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0.27396311263599826</v>
-      </c>
-      <c r="I5" s="1">
-        <v>9.1898468115879481</v>
+      <c r="A5">
+        <v>0.95393375422514237</v>
+      </c>
+      <c r="B5">
+        <v>0.95346111447738791</v>
+      </c>
+      <c r="C5">
+        <v>0.74255233304928225</v>
+      </c>
+      <c r="D5">
+        <v>0.12673378908994656</v>
+      </c>
+      <c r="E5">
+        <v>0.18891389578672835</v>
+      </c>
+      <c r="F5">
+        <v>5.0261924800702671</v>
+      </c>
+      <c r="G5">
+        <v>6.3928741424505615</v>
+      </c>
+      <c r="H5">
+        <v>0.27255939737010748</v>
+      </c>
+      <c r="I5">
+        <v>9.2429704710172356</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>0.96037411969893072</v>
-      </c>
-      <c r="B6" s="1">
-        <v>0.96043501744742554</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.74681961211470593</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0.126168682493909</v>
-      </c>
-      <c r="E6" s="1">
-        <v>0.17237756619028</v>
-      </c>
-      <c r="F6" s="1">
-        <v>5.0665944282716362</v>
-      </c>
-      <c r="G6" s="1">
-        <v>6.2832624489870597</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0.25469507159435667</v>
-      </c>
-      <c r="I6" s="1">
-        <v>9.9294527888527355</v>
+      <c r="A6">
+        <v>0.96046104381406061</v>
+      </c>
+      <c r="B6">
+        <v>0.96031557721676697</v>
+      </c>
+      <c r="C6">
+        <v>0.74523168160882847</v>
+      </c>
+      <c r="D6">
+        <v>0.12658965752005041</v>
+      </c>
+      <c r="E6">
+        <v>0.17284517743781058</v>
+      </c>
+      <c r="F6">
+        <v>5.0968680194291247</v>
+      </c>
+      <c r="G6">
+        <v>6.3190848563082458</v>
+      </c>
+      <c r="H6">
+        <v>0.25415663621544105</v>
+      </c>
+      <c r="I6">
+        <v>9.8881362816499898</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>0.96531139227479534</v>
-      </c>
-      <c r="B7" s="1">
-        <v>0.96531599073735075</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.74925312423421531</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0.1263931479761744</v>
-      </c>
-      <c r="E7" s="1">
-        <v>0.16083197550471984</v>
-      </c>
-      <c r="F7" s="1">
-        <v>5.1395859181169206</v>
-      </c>
-      <c r="G7" s="1">
-        <v>6.2912552008982372</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0.24085882907051515</v>
-      </c>
-      <c r="I7" s="1">
-        <v>10.341223080671048</v>
+      <c r="A7">
+        <v>0.96533875037556904</v>
+      </c>
+      <c r="B7">
+        <v>0.96510089976048574</v>
+      </c>
+      <c r="C7">
+        <v>0.7466610880830018</v>
+      </c>
+      <c r="D7">
+        <v>0.12664089283648222</v>
+      </c>
+      <c r="E7">
+        <v>0.16003247175370428</v>
+      </c>
+      <c r="F7">
+        <v>5.280830499570909</v>
+      </c>
+      <c r="G7">
+        <v>6.3119183569278681</v>
+      </c>
+      <c r="H7">
+        <v>0.240928705529045</v>
+      </c>
+      <c r="I7">
+        <v>10.384633910134561</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>0.96914850693760424</v>
-      </c>
-      <c r="B8" s="1">
-        <v>0.96909439946071485</v>
-      </c>
-      <c r="C8" s="1">
-        <v>0.75044609586954891</v>
-      </c>
-      <c r="D8" s="1">
-        <v>0.12598464131146955</v>
-      </c>
-      <c r="E8" s="1">
-        <v>0.15017033950330638</v>
-      </c>
-      <c r="F8" s="1">
-        <v>5.2173537386226876</v>
-      </c>
-      <c r="G8" s="1">
-        <v>6.2890527936332248</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0.23033342073049035</v>
-      </c>
-      <c r="I8" s="1">
-        <v>10.633717209275218</v>
+      <c r="A8">
+        <v>0.96913468275928971</v>
+      </c>
+      <c r="B8">
+        <v>0.96890725176489312</v>
+      </c>
+      <c r="C8">
+        <v>0.74438470384592392</v>
+      </c>
+      <c r="D8">
+        <v>0.12611686720011425</v>
+      </c>
+      <c r="E8">
+        <v>0.149911853692693</v>
+      </c>
+      <c r="F8">
+        <v>5.3594920739711016</v>
+      </c>
+      <c r="G8">
+        <v>6.2861921211834613</v>
+      </c>
+      <c r="H8">
+        <v>0.23021232367931166</v>
+      </c>
+      <c r="I8">
+        <v>10.604419955218264</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>0.97206881310453719</v>
-      </c>
-      <c r="B9" s="1">
-        <v>0.97197865380271276</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0.75115788308487197</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.12645969353328768</v>
-      </c>
-      <c r="E9" s="1">
-        <v>0.14127489225654133</v>
-      </c>
-      <c r="F9" s="1">
-        <v>5.3018561754738451</v>
-      </c>
-      <c r="G9" s="1">
-        <v>6.2226795124860761</v>
-      </c>
-      <c r="H9" s="1">
-        <v>0.17367179308453884</v>
-      </c>
-      <c r="I9" s="1">
-        <v>10.80497891932478</v>
+      <c r="A9">
+        <v>0.97224871061648088</v>
+      </c>
+      <c r="B9">
+        <v>0.97206584487137604</v>
+      </c>
+      <c r="C9">
+        <v>0.74175970875182884</v>
+      </c>
+      <c r="D9">
+        <v>0.12533652573220008</v>
+      </c>
+      <c r="E9">
+        <v>0.14139309213742968</v>
+      </c>
+      <c r="F9">
+        <v>5.3878967411314429</v>
+      </c>
+      <c r="G9">
+        <v>6.2280526697686707</v>
+      </c>
+      <c r="H9">
+        <v>0.17352531405670857</v>
+      </c>
+      <c r="I9">
+        <v>10.764658931747011</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>0.97451471479870899</v>
-      </c>
-      <c r="B10" s="1">
-        <v>0.97449608183469161</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0.75635654980847278</v>
-      </c>
-      <c r="D10" s="1">
-        <v>0.12709178220732625</v>
-      </c>
-      <c r="E10" s="1">
-        <v>0.13406522235930263</v>
-      </c>
-      <c r="F10" s="1">
-        <v>5.4694862352545819</v>
-      </c>
-      <c r="G10" s="1">
-        <v>6.2368621511618194</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0.16657931752571442</v>
-      </c>
-      <c r="I10" s="1">
-        <v>10.988627687016608</v>
+      <c r="A10">
+        <v>0.97471370967484183</v>
+      </c>
+      <c r="B10">
+        <v>0.97459741659315213</v>
+      </c>
+      <c r="C10">
+        <v>0.74171246864432305</v>
+      </c>
+      <c r="D10">
+        <v>0.12528590373590107</v>
+      </c>
+      <c r="E10">
+        <v>0.13435700260525779</v>
+      </c>
+      <c r="F10">
+        <v>5.4083744227532229</v>
+      </c>
+      <c r="G10">
+        <v>6.250222429340953</v>
+      </c>
+      <c r="H10">
+        <v>0.16643949457952356</v>
+      </c>
+      <c r="I10">
+        <v>10.904302946630111</v>
       </c>
     </row>
   </sheetData>
